--- a/测试集/泛用性验收_v3/W3/W3_反馈_财务部.xlsx
+++ b/测试集/泛用性验收_v3/W3/W3_反馈_财务部.xlsx
@@ -116,9 +116,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -495,18 +493,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -556,8 +544,10 @@
           <t>计划数</t>
         </is>
       </c>
-      <c r="F2" s="1" t="n">
-        <v>15</v>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>完成数</t>
+        </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
@@ -569,29 +559,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>组织安全培训演练</t>
+          <t>完成年度预算编制</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>综合办公室</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <f>F3/E3</f>
@@ -601,12 +591,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A006</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>成本合计核算</t>
+          <t>组织安全培训演练</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -616,17 +606,209 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <f>F4/E4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>设备巡检维护</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>工程技术部</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <f>F5/E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>季度报表汇总</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>安全管理部</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G6">
+        <f>F6/E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>完成资料汇总</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>综合办公室</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>35</v>
+      </c>
+      <c r="G7">
+        <f>F7/E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A006</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>成本合计核算</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>财务部</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="n">
+        <v>48</v>
+      </c>
+      <c r="G8">
+        <f>F8/E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A007</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>供应商评估审查</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>工程技术部</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" t="n">
+        <v>63</v>
+      </c>
+      <c r="G9">
+        <f>F9/E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A008</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>新员工入职办理</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>安全管理部</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>80</v>
+      </c>
+      <c r="F10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G10">
+        <f>F10/E10</f>
         <v/>
       </c>
     </row>
@@ -635,7 +817,7 @@
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G3:G4">
+  <conditionalFormatting sqref="G3:G10">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0.5</formula>
     </cfRule>

--- a/测试集/泛用性验收_v3/W3/W3_反馈_财务部.xlsx
+++ b/测试集/泛用性验收_v3/W3/W3_反馈_财务部.xlsx
@@ -116,7 +116,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -493,156 +495,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>任务名称</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>基本信息</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>进度</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>任务执行情况统计表</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>责任单位</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>完成时限</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>计划数</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>完成数</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>完成率</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>填报说明：请各单位如实填报执行进度。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>完成年度预算编制</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>综合办公室</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <f>F3/E3</f>
-        <v/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>任务名称</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>基本信息</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>进度</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>组织安全培训演练</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G4">
-        <f>F4/E4</f>
-        <v/>
-      </c>
+      <c r="A4" s="1" t="inlineStr"/>
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>责任单位</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>完成时限</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>计划数</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>完成数</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>完成率</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>设备巡检维护</t>
+          <t>组织安全培训演练</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>工程技术部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
         <v>15</v>
@@ -655,169 +607,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>A006</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>季度报表汇总</t>
+          <t>成本合计核算</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>安全管理部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G6">
         <f>F6/E6</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>完成资料汇总</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>综合办公室</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>50</v>
-      </c>
-      <c r="F7" t="n">
-        <v>35</v>
-      </c>
-      <c r="G7">
-        <f>F7/E7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A006</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>成本合计核算</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" t="n">
-        <v>48</v>
-      </c>
-      <c r="G8">
-        <f>F8/E8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A007</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>供应商评估审查</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>工程技术部</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>70</v>
-      </c>
-      <c r="F9" t="n">
-        <v>63</v>
-      </c>
-      <c r="G9">
-        <f>F9/E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A008</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>新员工入职办理</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>安全管理部</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>80</v>
-      </c>
-      <c r="F10" t="n">
-        <v>80</v>
-      </c>
-      <c r="G10">
-        <f>F10/E10</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:G1"/>
+  <mergeCells count="4">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G3:G10">
+  <conditionalFormatting sqref="G5:G6">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0.5</formula>
     </cfRule>
